--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -249,6 +249,10 @@
   </si>
   <si>
     <t>1001,1002,1003,1004,1005,1013</t>
+  </si>
+  <si>
+    <t>春之山脉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -767,7 +771,7 @@
         <v>4001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -794,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="O5" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P5" s="1">
         <v>0</v>
@@ -829,7 +833,7 @@
         <v>102</v>
       </c>
       <c r="L6" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="1" t="b">
         <v>0</v>
@@ -838,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P6" s="1">
         <v>0</v>
@@ -873,7 +877,7 @@
         <v>102</v>
       </c>
       <c r="L7" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="1" t="b">
         <v>0</v>
@@ -882,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O7" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P7" s="1">
         <v>0</v>
@@ -917,7 +921,7 @@
         <v>102</v>
       </c>
       <c r="L8" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="1" t="b">
         <v>0</v>
@@ -926,7 +930,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P8" s="1">
         <v>0</v>
@@ -961,7 +965,7 @@
         <v>102</v>
       </c>
       <c r="L9" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="1" t="b">
         <v>0</v>
@@ -970,7 +974,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P9" s="1">
         <v>0</v>
@@ -1005,7 +1009,7 @@
         <v>102</v>
       </c>
       <c r="L10" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="1" t="b">
         <v>0</v>
@@ -1014,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P10" s="1">
         <v>0</v>
@@ -1049,7 +1053,7 @@
         <v>102</v>
       </c>
       <c r="L11" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="1" t="b">
         <v>0</v>
@@ -1058,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
@@ -1093,7 +1097,7 @@
         <v>102</v>
       </c>
       <c r="L12" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="1" t="b">
         <v>0</v>
@@ -1102,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P12" s="1">
         <v>0</v>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="69">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -253,6 +253,10 @@
   <si>
     <t>春之山脉</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>skyDisplay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -594,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.375" style="1" customWidth="1"/>
@@ -605,7 +609,7 @@
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -613,7 +617,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -654,7 +658,7 @@
         <v>23</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>22</v>
@@ -666,10 +670,13 @@
         <v>22</v>
       </c>
       <c r="R2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -704,28 +711,31 @@
         <v>13</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
@@ -736,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>5.7</v>
+        <v>5.7426000000000004</v>
       </c>
       <c r="J4" s="1">
         <v>102</v>
@@ -748,22 +758,25 @@
         <v>1</v>
       </c>
       <c r="M4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="1">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
         <v>12</v>
       </c>
-      <c r="P4" s="1">
-        <v>0</v>
-      </c>
       <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
@@ -777,10 +790,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>5.7</v>
+        <v>5.7426000000000004</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>59</v>
@@ -792,9 +805,9 @@
         <v>1</v>
       </c>
       <c r="M5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O5" s="1">
@@ -804,10 +817,13 @@
         <v>0</v>
       </c>
       <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
@@ -821,10 +837,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="1">
-        <v>5.7</v>
+        <v>5.7426000000000004</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>60</v>
@@ -833,12 +849,12 @@
         <v>102</v>
       </c>
       <c r="L6" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O6" s="1">
@@ -848,10 +864,13 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>35</v>
       </c>
@@ -865,10 +884,10 @@
         <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>5.7</v>
+        <v>5.7426000000000004</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>61</v>
@@ -877,12 +896,12 @@
         <v>102</v>
       </c>
       <c r="L7" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O7" s="1">
@@ -892,10 +911,13 @@
         <v>0</v>
       </c>
       <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
@@ -909,10 +931,10 @@
         <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>5.7</v>
+        <v>5.7426000000000004</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>62</v>
@@ -921,12 +943,12 @@
         <v>102</v>
       </c>
       <c r="L8" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N8" s="1">
+      <c r="N8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O8" s="1">
@@ -936,10 +958,13 @@
         <v>0</v>
       </c>
       <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>42</v>
       </c>
@@ -953,10 +978,10 @@
         <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>5.7</v>
+        <v>5.7426000000000004</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>63</v>
@@ -965,12 +990,12 @@
         <v>102</v>
       </c>
       <c r="L9" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N9" s="1">
+      <c r="N9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O9" s="1">
@@ -980,10 +1005,13 @@
         <v>0</v>
       </c>
       <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>46</v>
       </c>
@@ -997,10 +1025,10 @@
         <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>5.7</v>
+        <v>5.7426000000000004</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>64</v>
@@ -1009,12 +1037,12 @@
         <v>102</v>
       </c>
       <c r="L10" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O10" s="1">
@@ -1024,10 +1052,13 @@
         <v>0</v>
       </c>
       <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>50</v>
       </c>
@@ -1041,10 +1072,10 @@
         <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>5.7</v>
+        <v>5.7426000000000004</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>65</v>
@@ -1053,12 +1084,12 @@
         <v>102</v>
       </c>
       <c r="L11" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N11" s="1">
+      <c r="N11" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O11" s="1">
@@ -1068,10 +1099,13 @@
         <v>0</v>
       </c>
       <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>54</v>
       </c>
@@ -1085,10 +1119,10 @@
         <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>5.7</v>
+        <v>5.7426000000000004</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>66</v>
@@ -1097,12 +1131,12 @@
         <v>102</v>
       </c>
       <c r="L12" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="O12" s="1">
@@ -1112,6 +1146,9 @@
         <v>0</v>
       </c>
       <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
         <v>22</v>
       </c>
     </row>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -820,7 +820,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
@@ -1055,7 +1055,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -1102,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="R11" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
@@ -1149,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="1">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -256,6 +256,10 @@
   </si>
   <si>
     <t>skyDisplay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102,102,102,102</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -306,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -318,6 +322,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -606,7 +613,8 @@
     <col min="3" max="5" width="12.25" style="1" customWidth="1"/>
     <col min="6" max="8" width="9" style="1"/>
     <col min="9" max="9" width="24.25" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="10" max="10" width="15.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
@@ -645,7 +653,7 @@
       <c r="I2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="5" t="s">
         <v>24</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -704,7 +712,7 @@
       <c r="I3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="K3" s="1" t="s">
@@ -751,7 +759,7 @@
       <c r="H4" s="1">
         <v>5.7426000000000004</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="5">
         <v>102</v>
       </c>
       <c r="L4" s="1" t="b">
@@ -798,8 +806,8 @@
       <c r="I5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J5" s="1">
-        <v>102</v>
+      <c r="J5" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="L5" s="1" t="b">
         <v>1</v>
@@ -845,7 +853,7 @@
       <c r="I6" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="5">
         <v>102</v>
       </c>
       <c r="L6" s="1" t="b">
@@ -892,7 +900,7 @@
       <c r="I7" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="5">
         <v>102</v>
       </c>
       <c r="L7" s="1" t="b">
@@ -939,7 +947,7 @@
       <c r="I8" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="5">
         <v>102</v>
       </c>
       <c r="L8" s="1" t="b">
@@ -986,7 +994,7 @@
       <c r="I9" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="5">
         <v>102</v>
       </c>
       <c r="L9" s="1" t="b">
@@ -1033,7 +1041,7 @@
       <c r="I10" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="5">
         <v>102</v>
       </c>
       <c r="L10" s="1" t="b">
@@ -1080,7 +1088,7 @@
       <c r="I11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="5">
         <v>102</v>
       </c>
       <c r="L11" s="1" t="b">
@@ -1127,7 +1135,7 @@
       <c r="I12" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="5">
         <v>102</v>
       </c>
       <c r="L12" s="1" t="b">

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -259,7 +259,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>102,102,102,102</t>
+    <t>102,102</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="FightMapData" sheetId="1" r:id="rId1"/>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="1">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -875,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
@@ -969,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="1">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="1">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
@@ -1063,7 +1063,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="1">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="R11" s="1">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="FightMapData" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="70">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,9 +52,6 @@
     <t>fightBGMName</t>
   </si>
   <si>
-    <t>offsetY</t>
-  </si>
-  <si>
     <t>float</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -261,6 +258,9 @@
   <si>
     <t>102,102</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙漠废墟</t>
   </si>
 </sst>
 </file>
@@ -605,27 +605,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
     <col min="3" max="5" width="12.25" style="1" customWidth="1"/>
-    <col min="6" max="8" width="9" style="1"/>
-    <col min="9" max="9" width="24.25" style="4" customWidth="1"/>
-    <col min="10" max="10" width="15.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="6" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="24.25" style="4" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,46 +645,43 @@
         <v>3</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>24</v>
+        <v>9</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -704,22 +701,22 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>14</v>
@@ -739,13 +736,10 @@
       <c r="R3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S3" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
@@ -754,68 +748,65 @@
         <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
-        <v>5.7426000000000004</v>
-      </c>
-      <c r="J4" s="5">
+        <v>-8.52</v>
+      </c>
+      <c r="I4" s="5">
         <v>102</v>
       </c>
+      <c r="K4" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="L4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="M4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
         <v>0</v>
       </c>
       <c r="O4" s="1">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P4" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="1">
-        <v>0</v>
-      </c>
-      <c r="R4" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2">
         <v>4001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
-        <v>5.7426000000000004</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>69</v>
+        <v>-8.52</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="L5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="M5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
         <v>0</v>
       </c>
       <c r="O5" s="1">
@@ -825,44 +816,41 @@
         <v>0</v>
       </c>
       <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="2">
         <v>4002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>5.7426000000000004</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J6" s="5">
+        <v>-8.52</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="5">
         <v>102</v>
       </c>
+      <c r="K6" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="L6" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N6" s="1" t="b">
+      <c r="N6" s="1">
         <v>0</v>
       </c>
       <c r="O6" s="1">
@@ -872,44 +860,41 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2">
         <v>4003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>5.7426000000000004</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J7" s="5">
+        <v>-8.52</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="5">
         <v>102</v>
       </c>
+      <c r="K7" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="L7" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N7" s="1" t="b">
+      <c r="N7" s="1">
         <v>0</v>
       </c>
       <c r="O7" s="1">
@@ -919,44 +904,41 @@
         <v>0</v>
       </c>
       <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2">
         <v>4004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" s="1">
         <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
-        <v>5.7426000000000004</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="5">
+        <v>-8.52</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="5">
         <v>102</v>
       </c>
+      <c r="K8" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="L8" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N8" s="1" t="b">
+      <c r="N8" s="1">
         <v>0</v>
       </c>
       <c r="O8" s="1">
@@ -966,44 +948,41 @@
         <v>0</v>
       </c>
       <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="2">
         <v>4005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" s="1">
         <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>5.7426000000000004</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="J9" s="5">
+        <v>-8.52</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="5">
         <v>102</v>
       </c>
+      <c r="K9" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="L9" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N9" s="1" t="b">
+      <c r="N9" s="1">
         <v>0</v>
       </c>
       <c r="O9" s="1">
@@ -1013,44 +992,41 @@
         <v>0</v>
       </c>
       <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="B10" s="2">
         <v>4006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="F10" s="1">
         <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>5.7426000000000004</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" s="5">
+        <v>-8.52</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="5">
         <v>102</v>
       </c>
+      <c r="K10" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="L10" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N10" s="1" t="b">
+      <c r="N10" s="1">
         <v>0</v>
       </c>
       <c r="O10" s="1">
@@ -1060,44 +1036,41 @@
         <v>0</v>
       </c>
       <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2">
         <v>4007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>5.7426000000000004</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" s="5">
+        <v>-8.52</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="5">
         <v>102</v>
       </c>
+      <c r="K11" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="L11" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N11" s="1" t="b">
+      <c r="N11" s="1">
         <v>0</v>
       </c>
       <c r="O11" s="1">
@@ -1107,44 +1080,41 @@
         <v>0</v>
       </c>
       <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2">
         <v>4008</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <v>5.7426000000000004</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="J12" s="5">
+        <v>-8.52</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I12" s="5">
         <v>102</v>
       </c>
+      <c r="K12" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="L12" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="N12" s="1" t="b">
+      <c r="N12" s="1">
         <v>0</v>
       </c>
       <c r="O12" s="1">
@@ -1154,9 +1124,6 @@
         <v>0</v>
       </c>
       <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
         <v>30</v>
       </c>
     </row>
@@ -1177,10 +1144,10 @@
         <v>4001</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="E3" s="2">
         <v>4</v>
@@ -1189,10 +1156,10 @@
         <v>40000</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -1206,10 +1173,10 @@
         <v>4002</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E4" s="2">
         <v>4</v>
@@ -1218,10 +1185,10 @@
         <v>40100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -1235,10 +1202,10 @@
         <v>4003</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E5" s="2">
         <v>4</v>
@@ -1247,10 +1214,10 @@
         <v>40200</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
@@ -1264,10 +1231,10 @@
         <v>4004</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="E6" s="2">
         <v>4</v>
@@ -1279,7 +1246,7 @@
         <v>4014</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
@@ -1293,10 +1260,10 @@
         <v>4005</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="E7" s="2">
         <v>4</v>
@@ -1305,10 +1272,10 @@
         <v>40400</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -1322,10 +1289,10 @@
         <v>4006</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="E8" s="2">
         <v>4</v>
@@ -1334,10 +1301,10 @@
         <v>40500</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
@@ -1351,10 +1318,10 @@
         <v>4007</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="E9" s="2">
         <v>4</v>
@@ -1363,10 +1330,10 @@
         <v>40600</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -1380,10 +1347,10 @@
         <v>4008</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="E10" s="2">
         <v>4</v>
@@ -1392,10 +1359,10 @@
         <v>40700</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="82">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -261,6 +261,46 @@
   </si>
   <si>
     <t>沙漠废墟</t>
+  </si>
+  <si>
+    <t>白天</t>
+  </si>
+  <si>
+    <t>黄昏</t>
+  </si>
+  <si>
+    <t>黎明</t>
+  </si>
+  <si>
+    <t>晚上</t>
+  </si>
+  <si>
+    <t>室内晚上</t>
+  </si>
+  <si>
+    <t>室内黎明</t>
+  </si>
+  <si>
+    <t>室内白天</t>
+  </si>
+  <si>
+    <t>室内黄昏</t>
+  </si>
+  <si>
+    <t>dayEnvironmentDataName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duskEnvironmentDataName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dawnEnvironmentDataName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nightEnvironmentDataName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -605,19 +645,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="5" width="12.25" style="1" customWidth="1"/>
-    <col min="6" max="7" width="9" style="1"/>
+    <col min="2" max="2" width="12.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.75" style="1" customWidth="1"/>
+    <col min="6" max="7" width="9" style="1" customWidth="1"/>
     <col min="8" max="8" width="24.25" style="4" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.125" style="5" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -625,7 +667,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -680,8 +722,20 @@
       <c r="R2" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="S2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -736,8 +790,20 @@
       <c r="R3" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
@@ -774,8 +840,20 @@
       <c r="Q4" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
@@ -818,8 +896,20 @@
       <c r="Q5" s="1">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -862,8 +952,20 @@
       <c r="Q6" s="1">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S6" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>34</v>
       </c>
@@ -906,8 +1008,20 @@
       <c r="Q7" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>38</v>
       </c>
@@ -950,8 +1064,20 @@
       <c r="Q8" s="1">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
@@ -994,8 +1120,20 @@
       <c r="Q9" s="1">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>69</v>
       </c>
@@ -1038,8 +1176,20 @@
       <c r="Q10" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
@@ -1082,8 +1232,20 @@
       <c r="Q11" s="1">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>53</v>
       </c>
@@ -1125,6 +1287,18 @@
       </c>
       <c r="Q12" s="1">
         <v>30</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="96">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -224,30 +224,6 @@
     <t>items</t>
   </si>
   <si>
-    <t>1001,1002,1003,1004,1005,1006</t>
-  </si>
-  <si>
-    <t>1001,1002,1003,1004,1005,1007</t>
-  </si>
-  <si>
-    <t>1001,1002,1003,1004,1005,1008</t>
-  </si>
-  <si>
-    <t>1001,1002,1003,1004,1005,1009</t>
-  </si>
-  <si>
-    <t>1001,1002,1003,1004,1005,1010</t>
-  </si>
-  <si>
-    <t>1001,1002,1003,1004,1005,1011</t>
-  </si>
-  <si>
-    <t>1001,1002,1003,1004,1005,1012</t>
-  </si>
-  <si>
-    <t>1001,1002,1003,1004,1005,1013</t>
-  </si>
-  <si>
     <t>春之山脉</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -256,13 +232,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>102,102</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>沙漠废墟</t>
-  </si>
-  <si>
     <t>白天</t>
   </si>
   <si>
@@ -301,6 +270,86 @@
   <si>
     <t>nightEnvironmentDataName</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>春之山脉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>瀑布洞穴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏之丛林</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>和风海岸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙漠废墟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>秋风之谷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬之雪原</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>极寒冰隙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>110,111,112,113,114</t>
+  </si>
+  <si>
+    <t>120,121,122,123,124</t>
+  </si>
+  <si>
+    <t>130,131,132,133,134</t>
+  </si>
+  <si>
+    <t>140,141,142,143,144</t>
+  </si>
+  <si>
+    <t>150,151,152,153,154</t>
+  </si>
+  <si>
+    <t>160,161,162,163,164</t>
+  </si>
+  <si>
+    <t>170,171,172,173,174</t>
+  </si>
+  <si>
+    <t>180,181,182,183,184</t>
+  </si>
+  <si>
+    <t>201,105,241,202,296,203,297,204,104,274,273,207,280,208</t>
+  </si>
+  <si>
+    <t>278,210,201,211,213,214,286,274,216,205,234,296,3003,218</t>
+  </si>
+  <si>
+    <t>287,102,291,220,293,228,221,105,222,203,3005,239,223,280,270,251,238,224,296</t>
+  </si>
+  <si>
+    <t>225,200,213,278,227,272,228,214,229,297,230,205,282,296,232,290,255,234,265</t>
+  </si>
+  <si>
+    <t>297,223,236,212,237,104,218,296,203,238,254,239,214,289,3005,240,288,241,294,274,280,259,285</t>
+  </si>
+  <si>
+    <t>284,296,244,200,278,245,214,255,246,292,247,3005,281,204,256,224,248,264,275,250,229,274</t>
+  </si>
+  <si>
+    <t>251,223,269,208,290,211,253,200,261,254,288,255,236,256,246,257,270,258,285,259,279,245</t>
+  </si>
+  <si>
+    <t>260,261,232,292,272,296,285,263,253,264,293,265,241,237,267,257,268,246</t>
   </si>
 </sst>
 </file>
@@ -651,8 +700,8 @@
     <col min="1" max="1" width="16.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.25" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="6.75" style="1" hidden="1" customWidth="1"/>
     <col min="6" max="7" width="9" style="1" customWidth="1"/>
     <col min="8" max="8" width="24.25" style="4" customWidth="1"/>
     <col min="9" max="9" width="15.125" style="5" customWidth="1"/>
@@ -767,7 +816,7 @@
         <v>12</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>13</v>
@@ -791,16 +840,16 @@
         <v>19</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
@@ -841,27 +890,27 @@
         <v>22</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="U4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="B5" s="2">
         <v>4001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F5" s="1">
         <v>1</v>
@@ -870,10 +919,10 @@
         <v>-8.52</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>1</v>
@@ -897,21 +946,21 @@
         <v>23</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="V5" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="B6" s="2">
         <v>4002</v>
@@ -926,10 +975,10 @@
         <v>-8.52</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" s="5">
-        <v>102</v>
+        <v>89</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>1</v>
@@ -953,19 +1002,19 @@
         <v>24</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>34</v>
       </c>
@@ -973,7 +1022,7 @@
         <v>4003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="F7" s="1">
         <v>2</v>
@@ -982,10 +1031,10 @@
         <v>-8.52</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" s="5">
-        <v>102</v>
+        <v>90</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="K7" s="1" t="b">
         <v>1</v>
@@ -1009,19 +1058,19 @@
         <v>25</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>38</v>
       </c>
@@ -1029,7 +1078,7 @@
         <v>4004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F8" s="1">
         <v>2</v>
@@ -1038,10 +1087,10 @@
         <v>-8.52</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="5">
-        <v>102</v>
+        <v>91</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>1</v>
@@ -1065,21 +1114,21 @@
         <v>26</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B9" s="2">
         <v>4005</v>
@@ -1094,10 +1143,10 @@
         <v>-8.52</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="I9" s="5">
-        <v>102</v>
+        <v>92</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>1</v>
@@ -1121,27 +1170,27 @@
         <v>27</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B10" s="2">
         <v>4006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F10" s="1">
         <v>3</v>
@@ -1150,10 +1199,10 @@
         <v>-8.52</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="I10" s="5">
-        <v>102</v>
+        <v>93</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>1</v>
@@ -1177,21 +1226,21 @@
         <v>28</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="B11" s="2">
         <v>4007</v>
@@ -1206,10 +1255,10 @@
         <v>-8.52</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="I11" s="5">
-        <v>102</v>
+        <v>94</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="K11" s="1" t="b">
         <v>1</v>
@@ -1233,21 +1282,21 @@
         <v>29</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B12" s="2">
         <v>4008</v>
@@ -1262,10 +1311,10 @@
         <v>-8.52</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" s="5">
-        <v>102</v>
+        <v>95</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="K12" s="1" t="b">
         <v>1</v>
@@ -1289,16 +1338,16 @@
         <v>30</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:J10"/>
+  <dimension ref="B3:J35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -1544,6 +1593,180 @@
       <c r="J10" s="2">
         <v>5</v>
       </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="D14" s="1">
+        <v>260</v>
+      </c>
+      <c r="E14">
+        <f>D14</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="D15" s="1">
+        <v>261</v>
+      </c>
+      <c r="E15" t="str">
+        <f>E14&amp;","&amp;D15</f>
+        <v>260,261</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="D16" s="1">
+        <v>232</v>
+      </c>
+      <c r="E16" t="str">
+        <f t="shared" ref="E16:E36" si="0">E15&amp;","&amp;D16</f>
+        <v>260,261,232</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D17" s="1">
+        <v>292</v>
+      </c>
+      <c r="E17" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292</v>
+      </c>
+    </row>
+    <row r="18" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D18" s="1">
+        <v>272</v>
+      </c>
+      <c r="E18" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272</v>
+      </c>
+    </row>
+    <row r="19" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D19" s="1">
+        <v>296</v>
+      </c>
+      <c r="E19" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272,296</v>
+      </c>
+    </row>
+    <row r="20" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D20" s="1">
+        <v>285</v>
+      </c>
+      <c r="E20" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272,296,285</v>
+      </c>
+    </row>
+    <row r="21" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D21" s="1">
+        <v>263</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272,296,285,263</v>
+      </c>
+    </row>
+    <row r="22" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D22" s="1">
+        <v>253</v>
+      </c>
+      <c r="E22" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272,296,285,263,253</v>
+      </c>
+    </row>
+    <row r="23" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D23" s="1">
+        <v>264</v>
+      </c>
+      <c r="E23" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272,296,285,263,253,264</v>
+      </c>
+    </row>
+    <row r="24" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D24" s="1">
+        <v>293</v>
+      </c>
+      <c r="E24" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272,296,285,263,253,264,293</v>
+      </c>
+    </row>
+    <row r="25" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D25" s="1">
+        <v>265</v>
+      </c>
+      <c r="E25" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272,296,285,263,253,264,293,265</v>
+      </c>
+    </row>
+    <row r="26" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D26" s="1">
+        <v>241</v>
+      </c>
+      <c r="E26" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272,296,285,263,253,264,293,265,241</v>
+      </c>
+    </row>
+    <row r="27" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D27" s="1">
+        <v>237</v>
+      </c>
+      <c r="E27" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272,296,285,263,253,264,293,265,241,237</v>
+      </c>
+    </row>
+    <row r="28" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D28" s="1">
+        <v>267</v>
+      </c>
+      <c r="E28" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272,296,285,263,253,264,293,265,241,237,267</v>
+      </c>
+    </row>
+    <row r="29" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D29" s="1">
+        <v>257</v>
+      </c>
+      <c r="E29" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272,296,285,263,253,264,293,265,241,237,267,257</v>
+      </c>
+    </row>
+    <row r="30" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D30" s="1">
+        <v>268</v>
+      </c>
+      <c r="E30" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272,296,285,263,253,264,293,265,241,237,267,257,268</v>
+      </c>
+    </row>
+    <row r="31" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D31" s="1">
+        <v>246</v>
+      </c>
+      <c r="E31" t="str">
+        <f t="shared" si="0"/>
+        <v>260,261,232,292,272,296,285,263,253,264,293,265,241,237,267,257,268,246</v>
+      </c>
+    </row>
+    <row r="32" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D35" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="100">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -350,6 +350,22 @@
   </si>
   <si>
     <t>260,261,232,292,272,296,285,263,253,264,293,265,241,237,267,257,268,246</t>
+  </si>
+  <si>
+    <t>沙漠白天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙漠黄昏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙漠黎明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沙漠晚上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1114,16 +1130,16 @@
         <v>26</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -1226,16 +1242,16 @@
         <v>28</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -1282,16 +1298,16 @@
         <v>29</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -1617,7 +1633,7 @@
         <v>232</v>
       </c>
       <c r="E16" t="str">
-        <f t="shared" ref="E16:E36" si="0">E15&amp;","&amp;D16</f>
+        <f t="shared" ref="E16:E31" si="0">E15&amp;","&amp;D16</f>
         <v>260,261,232</v>
       </c>
     </row>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="109">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -46,12 +46,6 @@
     <t>fightMapObjName</t>
   </si>
   <si>
-    <t>exploreBGMName</t>
-  </si>
-  <si>
-    <t>fightBGMName</t>
-  </si>
-  <si>
     <t>float</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -224,10 +218,6 @@
     <t>items</t>
   </si>
   <si>
-    <t>春之山脉</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>skyDisplay</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -280,14 +270,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>夏之丛林</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>和风海岸</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>沙漠废墟</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -366,6 +348,52 @@
   <si>
     <t>沙漠晚上</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>春之山脉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏之丛林</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬之雪原</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>秋风之谷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fightBGMStr</t>
+  </si>
+  <si>
+    <t>bossBGMStr</t>
+  </si>
+  <si>
+    <t>exploreBGMStr</t>
+  </si>
+  <si>
+    <t>Boss战</t>
+  </si>
+  <si>
+    <t>战斗6</t>
+  </si>
+  <si>
+    <t>战斗7</t>
+  </si>
+  <si>
+    <t>战斗8</t>
+  </si>
+  <si>
+    <t>战斗3</t>
+  </si>
+  <si>
+    <t>战斗4</t>
+  </si>
+  <si>
+    <t>战斗1</t>
   </si>
 </sst>
 </file>
@@ -710,29 +738,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.25" style="1" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="6.75" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="9" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24.25" style="4" customWidth="1"/>
-    <col min="9" max="9" width="15.125" style="5" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="4" max="5" width="9" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.25" style="4" customWidth="1"/>
+    <col min="7" max="7" width="15.125" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -743,64 +769,67 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>23</v>
+        <v>7</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -811,28 +840,28 @@
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>13</v>
@@ -850,520 +879,604 @@
         <v>17</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="S3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="T3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <v>-8.52</v>
+      </c>
+      <c r="G4" s="5">
+        <v>102</v>
+      </c>
+      <c r="I4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>12</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>22</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1">
-        <v>-8.52</v>
-      </c>
-      <c r="I4" s="5">
-        <v>102</v>
-      </c>
-      <c r="K4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="1">
-        <v>0</v>
-      </c>
-      <c r="O4" s="1">
-        <v>12</v>
-      </c>
-      <c r="P4" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>22</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="B5" s="2">
         <v>4001</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-8.52</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>-8.52</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="K5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="P5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>23</v>
-      </c>
       <c r="S5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="T5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>62</v>
+      <c r="U5" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B6" s="2">
         <v>4002</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="1">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="1">
+      <c r="E6" s="1">
         <v>-8.52</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>81</v>
+      <c r="F6" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="K6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
         <v>0</v>
       </c>
       <c r="N6" s="1">
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
         <v>24</v>
       </c>
+      <c r="Q6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="S6" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2">
         <v>4003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="1">
+        <v>96</v>
+      </c>
+      <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="G7" s="1">
+      <c r="E7" s="1">
         <v>-8.52</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>82</v>
+      <c r="F7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="K7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
         <v>0</v>
       </c>
       <c r="N7" s="1">
         <v>0</v>
       </c>
       <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
         <v>25</v>
       </c>
+      <c r="Q7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="S7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="T7" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>62</v>
+      <c r="U7" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2">
         <v>4004</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="1">
+        <v>36</v>
+      </c>
+      <c r="D8" s="1">
         <v>2</v>
       </c>
-      <c r="G8" s="1">
+      <c r="E8" s="1">
         <v>-8.52</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="F8" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="K8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1">
-        <v>0</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0</v>
-      </c>
-      <c r="P8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>26</v>
+      <c r="R8" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B9" s="2">
         <v>4005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="1">
+        <v>98</v>
+      </c>
+      <c r="D9" s="1">
         <v>3</v>
       </c>
-      <c r="G9" s="1">
+      <c r="E9" s="1">
         <v>-8.52</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>84</v>
+      <c r="F9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
         <v>0</v>
       </c>
       <c r="N9" s="1">
         <v>0</v>
       </c>
       <c r="O9" s="1">
-        <v>0</v>
-      </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1">
         <v>27</v>
       </c>
+      <c r="Q9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="S9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="T9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>62</v>
+      <c r="U9" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B10" s="2">
         <v>4006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="1">
+        <v>71</v>
+      </c>
+      <c r="D10" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="E10" s="1">
         <v>-8.52</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="F10" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="S10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0</v>
-      </c>
-      <c r="P10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>28</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="T10" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B11" s="2">
         <v>4007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="1">
+        <v>97</v>
+      </c>
+      <c r="D11" s="1">
         <v>4</v>
       </c>
-      <c r="G11" s="1">
+      <c r="E11" s="1">
         <v>-8.52</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="F11" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>29</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="T11" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="K11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0</v>
-      </c>
-      <c r="P11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>29</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="T11" s="1" t="s">
+      <c r="U11" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="U11" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="V11" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B12" s="2">
         <v>4008</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="1">
+        <v>51</v>
+      </c>
+      <c r="D12" s="1">
         <v>4</v>
       </c>
-      <c r="G12" s="1">
+      <c r="E12" s="1">
         <v>-8.52</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>87</v>
+      <c r="F12" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1" t="b">
+        <v>0</v>
       </c>
       <c r="K12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
         <v>0</v>
       </c>
       <c r="N12" s="1">
         <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
         <v>30</v>
       </c>
+      <c r="Q12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="S12" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>64</v>
+        <v>105</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1383,10 +1496,10 @@
         <v>4001</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2">
         <v>4</v>
@@ -1395,10 +1508,10 @@
         <v>40000</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -1412,10 +1525,10 @@
         <v>4002</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E4" s="2">
         <v>4</v>
@@ -1424,10 +1537,10 @@
         <v>40100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -1441,10 +1554,10 @@
         <v>4003</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2">
         <v>4</v>
@@ -1453,10 +1566,10 @@
         <v>40200</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
@@ -1470,10 +1583,10 @@
         <v>4004</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2">
         <v>4</v>
@@ -1485,7 +1598,7 @@
         <v>4014</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
@@ -1499,10 +1612,10 @@
         <v>4005</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2">
         <v>4</v>
@@ -1511,10 +1624,10 @@
         <v>40400</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -1528,10 +1641,10 @@
         <v>4006</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2">
         <v>4</v>
@@ -1540,10 +1653,10 @@
         <v>40500</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
@@ -1557,10 +1670,10 @@
         <v>4007</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2">
         <v>4</v>
@@ -1569,10 +1682,10 @@
         <v>40600</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -1586,10 +1699,10 @@
         <v>4008</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2">
         <v>4</v>
@@ -1598,10 +1711,10 @@
         <v>40700</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="115">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -394,6 +394,24 @@
   </si>
   <si>
     <t>战斗1</t>
+  </si>
+  <si>
+    <t>footStepStr</t>
+  </si>
+  <si>
+    <t>沙地1</t>
+  </si>
+  <si>
+    <t>石路1</t>
+  </si>
+  <si>
+    <t>浅草1</t>
+  </si>
+  <si>
+    <t>土路雪2</t>
+  </si>
+  <si>
+    <t>冰面</t>
   </si>
 </sst>
 </file>
@@ -443,7 +461,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -454,7 +472,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -738,19 +755,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.25" style="1" customWidth="1"/>
     <col min="4" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.25" style="4" customWidth="1"/>
-    <col min="7" max="7" width="15.125" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="18.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.375" style="4" customWidth="1"/>
+    <col min="8" max="15" width="9" style="1"/>
+    <col min="16" max="16" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -758,7 +777,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,10 +793,10 @@
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H2" s="1" t="s">
@@ -828,8 +847,11 @@
       <c r="W2" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="X2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -845,10 +867,10 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -899,8 +921,11 @@
       <c r="W3" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X3" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -913,7 +938,7 @@
       <c r="E4" s="1">
         <v>-8.52</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>102</v>
       </c>
       <c r="I4" s="1" t="b">
@@ -958,8 +983,11 @@
       <c r="W4" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="X4" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>69</v>
       </c>
@@ -975,10 +1003,10 @@
       <c r="E5" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>75</v>
       </c>
       <c r="I5" s="1" t="b">
@@ -1023,8 +1051,11 @@
       <c r="W5" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="X5" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -1040,10 +1071,10 @@
       <c r="E6" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>76</v>
       </c>
       <c r="I6" s="1" t="b">
@@ -1088,8 +1119,11 @@
       <c r="W6" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="X6" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="57" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -1105,10 +1139,10 @@
       <c r="E7" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>77</v>
       </c>
       <c r="I7" s="1" t="b">
@@ -1153,8 +1187,11 @@
       <c r="W7" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="X7" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="57" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -1170,10 +1207,10 @@
       <c r="E8" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>78</v>
       </c>
       <c r="I8" s="1" t="b">
@@ -1218,8 +1255,11 @@
       <c r="W8" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="X8" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>72</v>
       </c>
@@ -1235,10 +1275,10 @@
       <c r="E9" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>79</v>
       </c>
       <c r="I9" s="1" t="b">
@@ -1283,8 +1323,11 @@
       <c r="W9" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="X9" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>71</v>
       </c>
@@ -1300,10 +1343,10 @@
       <c r="E10" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>80</v>
       </c>
       <c r="I10" s="1" t="b">
@@ -1348,8 +1391,11 @@
       <c r="W10" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="X10" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>73</v>
       </c>
@@ -1365,10 +1411,10 @@
       <c r="E11" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>81</v>
       </c>
       <c r="I11" s="1" t="b">
@@ -1413,8 +1459,11 @@
       <c r="W11" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="X11" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="57" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>74</v>
       </c>
@@ -1430,10 +1479,10 @@
       <c r="E12" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>82</v>
       </c>
       <c r="I12" s="1" t="b">
@@ -1477,6 +1526,9 @@
       </c>
       <c r="W12" s="1" t="s">
         <v>102</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -19,8 +19,35 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>作者</author>
+  </authors>
+  <commentList>
+    <comment ref="E3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Outside 0,
+Inside  1,
+Forest  2</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="116">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -412,13 +439,17 @@
   </si>
   <si>
     <t>冰面</t>
+  </si>
+  <si>
+    <t>weatherDisplayType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,6 +470,14 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -754,22 +793,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.25" style="1" customWidth="1"/>
-    <col min="4" max="5" width="9" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="4" customWidth="1"/>
-    <col min="8" max="15" width="9" style="1"/>
-    <col min="16" max="16" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="4" max="6" width="9" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.375" style="4" customWidth="1"/>
+    <col min="9" max="16" width="9" style="1"/>
+    <col min="17" max="17" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -777,7 +816,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -791,19 +830,19 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>20</v>
@@ -812,7 +851,7 @@
         <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>19</v>
@@ -824,7 +863,7 @@
         <v>19</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>18</v>
@@ -850,8 +889,11 @@
       <c r="X2" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="Y2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -865,129 +907,135 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B4" s="1">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
         <v>-8.52</v>
       </c>
-      <c r="G4" s="4">
+      <c r="H4" s="4">
         <v>102</v>
-      </c>
-      <c r="I4" s="1" t="b">
-        <v>1</v>
       </c>
       <c r="J4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="1">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
         <v>12</v>
       </c>
-      <c r="N4" s="1">
-        <v>0</v>
-      </c>
       <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
         <v>22</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>69</v>
       </c>
@@ -1001,24 +1049,24 @@
         <v>1</v>
       </c>
       <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="I5" s="1" t="b">
-        <v>1</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M5" s="1">
@@ -1028,34 +1076,37 @@
         <v>0</v>
       </c>
       <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
         <v>23</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="S5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="V5" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="W5" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="X5" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="Y5" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -1069,24 +1120,24 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="I6" s="1" t="b">
+      <c r="J6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J6" s="1" t="b">
-        <v>0</v>
-      </c>
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M6" s="1">
@@ -1096,34 +1147,37 @@
         <v>0</v>
       </c>
       <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
         <v>24</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="R6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="S6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="T6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="T6" s="1" t="s">
+      <c r="U6" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="V6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="V6" s="1" t="s">
+      <c r="W6" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="W6" s="1" t="s">
+      <c r="X6" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X6" s="1" t="s">
+      <c r="Y6" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="57" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="57" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -1137,24 +1191,24 @@
         <v>2</v>
       </c>
       <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="1" t="b">
+      <c r="J7" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J7" s="1" t="b">
-        <v>0</v>
-      </c>
       <c r="K7" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M7" s="1">
@@ -1164,34 +1218,37 @@
         <v>0</v>
       </c>
       <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
         <v>25</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="S7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="T7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="U7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="V7" s="1" t="s">
+      <c r="W7" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="W7" s="1" t="s">
+      <c r="X7" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X7" s="1" t="s">
+      <c r="Y7" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="57" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="57" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -1205,24 +1262,24 @@
         <v>2</v>
       </c>
       <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="1" t="b">
+      <c r="J8" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J8" s="1" t="b">
-        <v>0</v>
-      </c>
       <c r="K8" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L8" s="1">
+      <c r="L8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M8" s="1">
@@ -1232,34 +1289,37 @@
         <v>0</v>
       </c>
       <c r="O8" s="1">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1">
         <v>26</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="R8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="S8" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="T8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="U8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="V8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="V8" s="1" t="s">
+      <c r="W8" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="W8" s="1" t="s">
+      <c r="X8" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X8" s="1" t="s">
+      <c r="Y8" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>72</v>
       </c>
@@ -1273,24 +1333,24 @@
         <v>3</v>
       </c>
       <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="1" t="b">
+      <c r="J9" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J9" s="1" t="b">
-        <v>0</v>
-      </c>
       <c r="K9" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M9" s="1">
@@ -1300,34 +1360,37 @@
         <v>0</v>
       </c>
       <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1">
         <v>27</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="R9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="S9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="T9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="T9" s="1" t="s">
+      <c r="U9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="U9" s="2" t="s">
+      <c r="V9" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="V9" s="1" t="s">
+      <c r="W9" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="W9" s="1" t="s">
+      <c r="X9" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X9" s="1" t="s">
+      <c r="Y9" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>71</v>
       </c>
@@ -1341,24 +1404,24 @@
         <v>3</v>
       </c>
       <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="I10" s="1" t="b">
+      <c r="J10" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J10" s="1" t="b">
-        <v>0</v>
-      </c>
       <c r="K10" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M10" s="1">
@@ -1368,34 +1431,37 @@
         <v>0</v>
       </c>
       <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
         <v>28</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="T10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T10" s="1" t="s">
+      <c r="U10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="V10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="V10" s="1" t="s">
+      <c r="W10" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="W10" s="1" t="s">
+      <c r="X10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X10" s="1" t="s">
+      <c r="Y10" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>73</v>
       </c>
@@ -1409,24 +1475,24 @@
         <v>4</v>
       </c>
       <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="I11" s="1" t="b">
+      <c r="J11" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J11" s="1" t="b">
-        <v>0</v>
-      </c>
       <c r="K11" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L11" s="1">
+      <c r="L11" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M11" s="1">
@@ -1436,34 +1502,37 @@
         <v>0</v>
       </c>
       <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
         <v>29</v>
       </c>
-      <c r="Q11" s="1" t="s">
+      <c r="R11" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="R11" s="1" t="s">
+      <c r="S11" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="S11" s="1" t="s">
+      <c r="T11" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T11" s="1" t="s">
+      <c r="U11" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U11" s="2" t="s">
+      <c r="V11" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="V11" s="1" t="s">
+      <c r="W11" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="W11" s="1" t="s">
+      <c r="X11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X11" s="1" t="s">
+      <c r="Y11" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="57" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="57" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>74</v>
       </c>
@@ -1477,24 +1546,24 @@
         <v>4</v>
       </c>
       <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
         <v>-8.52</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I12" s="1" t="b">
+      <c r="J12" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="1" t="b">
-        <v>0</v>
-      </c>
       <c r="K12" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="M12" s="1">
@@ -1504,37 +1573,41 @@
         <v>0</v>
       </c>
       <c r="O12" s="1">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1">
         <v>30</v>
       </c>
-      <c r="Q12" s="1" t="s">
+      <c r="R12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="R12" s="1" t="s">
+      <c r="S12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="S12" s="1" t="s">
+      <c r="T12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="T12" s="1" t="s">
+      <c r="U12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="V12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="V12" s="1" t="s">
+      <c r="W12" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="W12" s="1" t="s">
+      <c r="X12" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="X12" s="1" t="s">
+      <c r="Y12" s="1" t="s">
         <v>114</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="117">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -442,6 +442,10 @@
   </si>
   <si>
     <t>weatherDisplayType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>endActionId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -794,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.375" style="1" customWidth="1"/>
@@ -803,12 +807,12 @@
     <col min="4" max="6" width="9" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.375" style="4" customWidth="1"/>
-    <col min="9" max="16" width="9" style="1"/>
-    <col min="17" max="17" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="9" max="17" width="9" style="1"/>
+    <col min="18" max="18" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -816,7 +820,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -866,7 +870,7 @@
         <v>19</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>18</v>
@@ -892,8 +896,11 @@
       <c r="Y2" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="Z2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -940,37 +947,40 @@
         <v>15</v>
       </c>
       <c r="P3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -1002,40 +1012,43 @@
         <v>0</v>
       </c>
       <c r="N4" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O4" s="1">
         <v>0</v>
       </c>
       <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1">
         <v>22</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>69</v>
       </c>
@@ -1079,34 +1092,37 @@
         <v>0</v>
       </c>
       <c r="P5" s="1">
-        <v>23</v>
-      </c>
-      <c r="R5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="V5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="W5" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="X5" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="X5" s="1" t="s">
+      <c r="Y5" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y5" s="1" t="s">
+      <c r="Z5" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -1150,34 +1166,37 @@
         <v>0</v>
       </c>
       <c r="P6" s="1">
-        <v>24</v>
-      </c>
-      <c r="R6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="T6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="T6" s="1" t="s">
+      <c r="U6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="U6" s="1" t="s">
+      <c r="V6" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="W6" s="1" t="s">
+      <c r="X6" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="X6" s="1" t="s">
+      <c r="Y6" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y6" s="1" t="s">
+      <c r="Z6" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="57" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="57" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -1221,34 +1240,37 @@
         <v>0</v>
       </c>
       <c r="P7" s="1">
-        <v>25</v>
-      </c>
-      <c r="R7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="T7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="U7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="U7" s="1" t="s">
+      <c r="V7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="W7" s="1" t="s">
+      <c r="X7" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="X7" s="1" t="s">
+      <c r="Y7" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y7" s="1" t="s">
+      <c r="Z7" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="57" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" ht="57" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -1292,34 +1314,37 @@
         <v>0</v>
       </c>
       <c r="P8" s="1">
-        <v>26</v>
-      </c>
-      <c r="R8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="T8" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="U8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="U8" s="1" t="s">
+      <c r="V8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="W8" s="1" t="s">
+      <c r="X8" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="X8" s="1" t="s">
+      <c r="Y8" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y8" s="1" t="s">
+      <c r="Z8" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>72</v>
       </c>
@@ -1363,34 +1388,37 @@
         <v>0</v>
       </c>
       <c r="P9" s="1">
-        <v>27</v>
-      </c>
-      <c r="R9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="T9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="T9" s="1" t="s">
+      <c r="U9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="U9" s="1" t="s">
+      <c r="V9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="V9" s="2" t="s">
+      <c r="W9" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="W9" s="1" t="s">
+      <c r="X9" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="X9" s="1" t="s">
+      <c r="Y9" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y9" s="1" t="s">
+      <c r="Z9" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>71</v>
       </c>
@@ -1434,34 +1462,37 @@
         <v>0</v>
       </c>
       <c r="P10" s="1">
-        <v>28</v>
-      </c>
-      <c r="R10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="T10" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="T10" s="1" t="s">
+      <c r="U10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="U10" s="1" t="s">
+      <c r="V10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V10" s="2" t="s">
+      <c r="W10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="W10" s="1" t="s">
+      <c r="X10" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="X10" s="1" t="s">
+      <c r="Y10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y10" s="1" t="s">
+      <c r="Z10" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>73</v>
       </c>
@@ -1505,34 +1536,37 @@
         <v>0</v>
       </c>
       <c r="P11" s="1">
-        <v>29</v>
-      </c>
-      <c r="R11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="S11" s="1" t="s">
+      <c r="T11" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="T11" s="1" t="s">
+      <c r="U11" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="U11" s="1" t="s">
+      <c r="V11" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V11" s="2" t="s">
+      <c r="W11" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="W11" s="1" t="s">
+      <c r="X11" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="X11" s="1" t="s">
+      <c r="Y11" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y11" s="1" t="s">
+      <c r="Z11" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="57" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" ht="57" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>74</v>
       </c>
@@ -1576,30 +1610,33 @@
         <v>0</v>
       </c>
       <c r="P12" s="1">
-        <v>30</v>
-      </c>
-      <c r="R12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="S12" s="1" t="s">
+      <c r="T12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="T12" s="1" t="s">
+      <c r="U12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="U12" s="1" t="s">
+      <c r="V12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="V12" s="2" t="s">
+      <c r="W12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="W12" s="1" t="s">
+      <c r="X12" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="X12" s="1" t="s">
+      <c r="Y12" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Y12" s="1" t="s">
+      <c r="Z12" s="1" t="s">
         <v>114</v>
       </c>
     </row>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -1225,7 +1225,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="1" t="b">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="1" t="b">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>1</v>
       </c>
       <c r="K11" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="1" t="b">
         <v>0</v>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="118">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -305,10 +305,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>冬之雪原</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>极寒冰隙</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -446,6 +442,14 @@
   </si>
   <si>
     <t>endActionId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冬之雪原</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>checkBeforeChapter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -798,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.375" style="1" customWidth="1"/>
@@ -807,12 +811,14 @@
     <col min="4" max="6" width="9" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.375" style="4" customWidth="1"/>
-    <col min="9" max="17" width="9" style="1"/>
-    <col min="18" max="18" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="1"/>
+    <col min="9" max="12" width="9" style="1"/>
+    <col min="13" max="13" width="18.375" style="1" customWidth="1"/>
+    <col min="14" max="18" width="9" style="1"/>
+    <col min="19" max="19" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -820,7 +826,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -873,7 +879,7 @@
         <v>19</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>18</v>
@@ -899,8 +905,11 @@
       <c r="Z2" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AA2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -914,7 +923,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
@@ -938,49 +947,52 @@
         <v>12</v>
       </c>
       <c r="M3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="Q3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="W3" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="X3" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="Y3" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z3" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA3" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -1021,34 +1033,37 @@
         <v>0</v>
       </c>
       <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1">
         <v>22</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="X4" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="Y4" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="42.75" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>69</v>
       </c>
@@ -1056,7 +1071,7 @@
         <v>4001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -1068,10 +1083,10 @@
         <v>-8.52</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J5" s="1" t="b">
         <v>1</v>
@@ -1095,34 +1110,37 @@
         <v>0</v>
       </c>
       <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="R5" s="1">
+        <v>23</v>
+      </c>
+      <c r="T5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="V5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="W5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="W5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="X5" s="1" t="s">
-        <v>108</v>
+      <c r="X5" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="42.75" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -1142,10 +1160,10 @@
         <v>-8.52</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J6" s="1" t="b">
         <v>1</v>
@@ -1171,32 +1189,35 @@
       <c r="Q6" s="1">
         <v>0</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="T6" s="1" t="s">
+      <c r="U6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U6" s="1" t="s">
+      <c r="V6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="V6" s="1" t="s">
+      <c r="W6" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="X6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="X6" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="Y6" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="57" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="57" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -1204,7 +1225,7 @@
         <v>4003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
@@ -1216,10 +1237,10 @@
         <v>-8.52</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J7" s="1" t="b">
         <v>1</v>
@@ -1231,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>0</v>
+        <v>4001</v>
       </c>
       <c r="N7" s="1">
         <v>0</v>
@@ -1245,32 +1266,35 @@
       <c r="Q7" s="1">
         <v>0</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="R7" s="1">
+        <v>24</v>
+      </c>
+      <c r="T7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="U7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="U7" s="1" t="s">
+      <c r="V7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="V7" s="1" t="s">
+      <c r="W7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>106</v>
+      <c r="X7" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="57" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="57" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -1290,10 +1314,10 @@
         <v>-8.52</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J8" s="1" t="b">
         <v>1</v>
@@ -1319,32 +1343,35 @@
       <c r="Q8" s="1">
         <v>0</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="U8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="V8" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="U8" s="1" t="s">
+      <c r="W8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="V8" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="W8" s="2" t="s">
+      <c r="X8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="X8" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="Y8" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" ht="71.25" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>72</v>
       </c>
@@ -1352,7 +1379,7 @@
         <v>4005</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D9" s="1">
         <v>3</v>
@@ -1364,10 +1391,10 @@
         <v>-8.52</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J9" s="1" t="b">
         <v>1</v>
@@ -1379,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <v>0</v>
+        <v>4003</v>
       </c>
       <c r="N9" s="1">
         <v>0</v>
@@ -1393,32 +1420,35 @@
       <c r="Q9" s="1">
         <v>0</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="R9" s="1">
+        <v>25</v>
+      </c>
+      <c r="T9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="T9" s="1" t="s">
+      <c r="U9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="U9" s="1" t="s">
+      <c r="V9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="V9" s="1" t="s">
+      <c r="W9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="W9" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>108</v>
+      <c r="X9" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" ht="71.25" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>71</v>
       </c>
@@ -1438,10 +1468,10 @@
         <v>-8.52</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J10" s="1" t="b">
         <v>1</v>
@@ -1467,40 +1497,43 @@
       <c r="Q10" s="1">
         <v>0</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="U10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="T10" s="1" t="s">
+      <c r="V10" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="U10" s="1" t="s">
+      <c r="W10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="V10" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="W10" s="2" t="s">
+      <c r="X10" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="Y10" s="1" t="s">
         <v>102</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="71.25" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="B11" s="2">
         <v>4007</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -1512,10 +1545,10 @@
         <v>-8.52</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J11" s="1" t="b">
         <v>1</v>
@@ -1526,8 +1559,8 @@
       <c r="L11" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="M11" s="1">
-        <v>0</v>
+      <c r="M11" s="2">
+        <v>4005</v>
       </c>
       <c r="N11" s="1">
         <v>0</v>
@@ -1541,34 +1574,37 @@
       <c r="Q11" s="1">
         <v>0</v>
       </c>
-      <c r="S11" s="1" t="s">
+      <c r="R11" s="1">
+        <v>26</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="U11" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="T11" s="1" t="s">
+      <c r="V11" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="U11" s="1" t="s">
+      <c r="W11" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="V11" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>104</v>
+      <c r="X11" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="57" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="57" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B12" s="2">
         <v>4008</v>
@@ -1586,10 +1622,10 @@
         <v>-8.52</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J12" s="1" t="b">
         <v>1</v>
@@ -1615,29 +1651,32 @@
       <c r="Q12" s="1">
         <v>0</v>
       </c>
-      <c r="S12" s="1" t="s">
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="T12" s="1" t="s">
+      <c r="U12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U12" s="1" t="s">
+      <c r="V12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="V12" s="1" t="s">
+      <c r="W12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="W12" s="2" t="s">
+      <c r="X12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="X12" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="Y12" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>114</v>
+        <v>101</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -1050,8 +1050,8 @@
       <c r="W4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="X4" s="2" t="s">
-        <v>36</v>
+      <c r="X4" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>106</v>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="128">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -450,6 +450,46 @@
   </si>
   <si>
     <t>checkBeforeChapter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分布有风属性、水属性怪物,适合穿戴冰属性、土属性装备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分布有火属性怪物,适合穿戴水属性装备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分布有土属性、水属性怪物,适合穿戴风属性、土属性装备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分布有风属性、水属性怪物,适合穿戴冰属性、水属性装备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分布有冰属性、土属性怪物,适合穿戴火属性、风属性装备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分布有火属性、土属性怪物,适合穿戴水属性、风属性装备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分布有冰属性、水属性怪物,适合穿戴火属性、土属性装备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分布有风属性、冰属性怪物,适合穿戴冰属性、火属性装备</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -802,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.375" style="1" customWidth="1"/>
@@ -811,14 +851,16 @@
     <col min="4" max="6" width="9" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.375" style="4" customWidth="1"/>
-    <col min="9" max="12" width="9" style="1"/>
-    <col min="13" max="13" width="18.375" style="1" customWidth="1"/>
-    <col min="14" max="18" width="9" style="1"/>
-    <col min="19" max="19" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="1"/>
+    <col min="9" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="20.25" style="1" customWidth="1"/>
+    <col min="11" max="13" width="9" style="1"/>
+    <col min="14" max="14" width="10.625" style="1" customWidth="1"/>
+    <col min="15" max="19" width="9" style="1"/>
+    <col min="20" max="20" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -826,7 +868,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -855,7 +897,7 @@
         <v>21</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>20</v>
@@ -864,7 +906,7 @@
         <v>20</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>19</v>
@@ -882,7 +924,7 @@
         <v>19</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>18</v>
@@ -908,8 +950,11 @@
       <c r="AA2" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="AB2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -938,61 +983,64 @@
         <v>10</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -1011,16 +1059,13 @@
       <c r="H4" s="4">
         <v>102</v>
       </c>
-      <c r="J4" s="1" t="b">
-        <v>1</v>
-      </c>
       <c r="K4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="1">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="N4" s="1">
@@ -1036,34 +1081,37 @@
         <v>0</v>
       </c>
       <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1">
         <v>22</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="Y4" s="1" t="s">
         <v>106</v>
       </c>
       <c r="Z4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA4" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>69</v>
       </c>
@@ -1088,16 +1136,16 @@
       <c r="H5" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J5" s="1" t="b">
-        <v>1</v>
+      <c r="J5" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="N5" s="1">
@@ -1110,37 +1158,40 @@
         <v>0</v>
       </c>
       <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
         <v>97</v>
       </c>
-      <c r="R5" s="1">
+      <c r="S5" s="1">
         <v>23</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U5" s="1" t="s">
+      <c r="V5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="V5" s="1" t="s">
+      <c r="W5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="W5" s="1" t="s">
+      <c r="X5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="X5" s="2" t="s">
+      <c r="Y5" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="Y5" s="1" t="s">
+      <c r="Z5" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="Z5" s="1" t="s">
+      <c r="AA5" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AA5" s="1" t="s">
+      <c r="AB5" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>70</v>
       </c>
@@ -1165,16 +1216,16 @@
       <c r="H6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="J6" s="1" t="b">
+      <c r="J6" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K6" s="1" t="b">
-        <v>0</v>
-      </c>
       <c r="L6" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="N6" s="1">
@@ -1192,32 +1243,35 @@
       <c r="R6" s="1">
         <v>0</v>
       </c>
-      <c r="T6" s="1" t="s">
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="U6" s="1" t="s">
+      <c r="V6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="V6" s="1" t="s">
+      <c r="W6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="W6" s="1" t="s">
+      <c r="X6" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="X6" s="2" t="s">
+      <c r="Y6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="Y6" s="1" t="s">
+      <c r="Z6" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="Z6" s="1" t="s">
+      <c r="AA6" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AA6" s="1" t="s">
+      <c r="AB6" s="1" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="57" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" ht="57" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -1242,21 +1296,21 @@
       <c r="H7" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="1" t="b">
-        <v>1</v>
+      <c r="J7" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="K7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L7" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
         <v>4001</v>
       </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
       <c r="O7" s="1">
         <v>0</v>
       </c>
@@ -1267,34 +1321,37 @@
         <v>0</v>
       </c>
       <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
         <v>24</v>
       </c>
-      <c r="T7" s="1" t="s">
+      <c r="U7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U7" s="1" t="s">
+      <c r="V7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="V7" s="1" t="s">
+      <c r="W7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="W7" s="1" t="s">
+      <c r="X7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="Y7" s="1" t="s">
+      <c r="Z7" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="Z7" s="1" t="s">
+      <c r="AA7" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AA7" s="1" t="s">
+      <c r="AB7" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="57" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" ht="57" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -1319,16 +1376,16 @@
       <c r="H8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="J8" s="1" t="b">
+      <c r="J8" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K8" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K8" s="1" t="b">
-        <v>0</v>
-      </c>
       <c r="L8" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="M8" s="1">
+      <c r="M8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="N8" s="1">
@@ -1346,32 +1403,35 @@
       <c r="R8" s="1">
         <v>0</v>
       </c>
-      <c r="T8" s="1" t="s">
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="U8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="U8" s="1" t="s">
+      <c r="V8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="V8" s="1" t="s">
+      <c r="W8" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="W8" s="1" t="s">
+      <c r="X8" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="X8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Y8" s="1" t="s">
+      <c r="Z8" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="Z8" s="1" t="s">
+      <c r="AA8" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AA8" s="1" t="s">
+      <c r="AB8" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>72</v>
       </c>
@@ -1396,21 +1456,21 @@
       <c r="H9" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="J9" s="1" t="b">
-        <v>1</v>
+      <c r="J9" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L9" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
         <v>4003</v>
       </c>
-      <c r="N9" s="1">
-        <v>0</v>
-      </c>
       <c r="O9" s="1">
         <v>0</v>
       </c>
@@ -1421,34 +1481,37 @@
         <v>0</v>
       </c>
       <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
         <v>25</v>
       </c>
-      <c r="T9" s="1" t="s">
+      <c r="U9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="U9" s="1" t="s">
+      <c r="V9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="V9" s="1" t="s">
+      <c r="W9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="W9" s="1" t="s">
+      <c r="X9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="X9" s="2" t="s">
+      <c r="Y9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="Y9" s="1" t="s">
+      <c r="Z9" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="Z9" s="1" t="s">
+      <c r="AA9" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AA9" s="1" t="s">
+      <c r="AB9" s="1" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>71</v>
       </c>
@@ -1473,16 +1536,16 @@
       <c r="H10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="J10" s="1" t="b">
+      <c r="J10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K10" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K10" s="1" t="b">
-        <v>0</v>
-      </c>
       <c r="L10" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="N10" s="1">
@@ -1500,32 +1563,35 @@
       <c r="R10" s="1">
         <v>0</v>
       </c>
-      <c r="T10" s="1" t="s">
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="U10" s="1" t="s">
+      <c r="V10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="V10" s="1" t="s">
+      <c r="W10" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="W10" s="1" t="s">
+      <c r="X10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="X10" s="2" t="s">
+      <c r="Y10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="Y10" s="1" t="s">
+      <c r="Z10" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="Z10" s="1" t="s">
+      <c r="AA10" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AA10" s="1" t="s">
+      <c r="AB10" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>116</v>
       </c>
@@ -1550,21 +1616,21 @@
       <c r="H11" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="J11" s="1" t="b">
-        <v>1</v>
+      <c r="J11" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="K11" s="1" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2">
         <v>4005</v>
       </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
       <c r="O11" s="1">
         <v>0</v>
       </c>
@@ -1575,34 +1641,37 @@
         <v>0</v>
       </c>
       <c r="R11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1">
         <v>26</v>
       </c>
-      <c r="T11" s="1" t="s">
+      <c r="U11" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="U11" s="1" t="s">
+      <c r="V11" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="V11" s="1" t="s">
+      <c r="W11" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="W11" s="1" t="s">
+      <c r="X11" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="X11" s="2" t="s">
+      <c r="Y11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="Y11" s="1" t="s">
+      <c r="Z11" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="Z11" s="1" t="s">
+      <c r="AA11" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AA11" s="1" t="s">
+      <c r="AB11" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="57" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" ht="57" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>73</v>
       </c>
@@ -1627,16 +1696,16 @@
       <c r="H12" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="J12" s="1" t="b">
+      <c r="J12" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K12" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K12" s="1" t="b">
-        <v>0</v>
-      </c>
       <c r="L12" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="M12" s="1">
+      <c r="M12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="N12" s="1">
@@ -1654,28 +1723,31 @@
       <c r="R12" s="1">
         <v>0</v>
       </c>
-      <c r="T12" s="1" t="s">
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="U12" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="U12" s="1" t="s">
+      <c r="V12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="V12" s="1" t="s">
+      <c r="W12" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="W12" s="1" t="s">
+      <c r="X12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="X12" s="2" t="s">
+      <c r="Y12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="Y12" s="1" t="s">
+      <c r="Z12" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="Z12" s="1" t="s">
+      <c r="AA12" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AA12" s="1" t="s">
+      <c r="AB12" s="1" t="s">
         <v>113</v>
       </c>
     </row>

--- a/Datas/FightMapDataList.xlsx
+++ b/Datas/FightMapDataList.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="136">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -389,54 +389,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>fightBGMStr</t>
-  </si>
-  <si>
-    <t>bossBGMStr</t>
-  </si>
-  <si>
-    <t>exploreBGMStr</t>
-  </si>
-  <si>
-    <t>Boss战</t>
-  </si>
-  <si>
-    <t>战斗6</t>
-  </si>
-  <si>
-    <t>战斗7</t>
-  </si>
-  <si>
-    <t>战斗8</t>
-  </si>
-  <si>
-    <t>战斗3</t>
-  </si>
-  <si>
-    <t>战斗4</t>
-  </si>
-  <si>
-    <t>战斗1</t>
-  </si>
-  <si>
-    <t>footStepStr</t>
-  </si>
-  <si>
-    <t>沙地1</t>
-  </si>
-  <si>
-    <t>石路1</t>
-  </si>
-  <si>
-    <t>浅草1</t>
-  </si>
-  <si>
-    <t>土路雪2</t>
-  </si>
-  <si>
-    <t>冰面</t>
-  </si>
-  <si>
     <t>weatherDisplayType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -491,6 +443,102 @@
   <si>
     <t>分布有风属性、冰属性怪物,适合穿戴冰属性、火属性装备</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exploreBGM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fightBGM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bossBGM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>footStep</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Footsteps_沙地1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Footsteps_石路1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Footsteps_浅草1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Footsteps_土路雪2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Footsteps_冰面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battle_战斗4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battle_Boss战</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battle_战斗1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battle_战斗8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battle_战斗3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battle_战斗6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battle_战斗7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explorer_春之山脉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explorer_瀑布洞穴</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explorer_夏之丛林</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explorer_和风海岸</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explorer_秋风之谷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explorer_沙漠废墟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explorer_冬之雪原</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Explorer_极寒冰隙</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -897,7 +945,7 @@
         <v>21</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>20</v>
@@ -968,7 +1016,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
@@ -983,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>56</v>
@@ -995,7 +1043,7 @@
         <v>12</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>13</v>
@@ -1007,7 +1055,7 @@
         <v>15</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>16</v>
@@ -1028,19 +1076,19 @@
         <v>68</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -1099,16 +1147,16 @@
         <v>60</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="42.75" x14ac:dyDescent="0.2">
@@ -1137,7 +1185,7 @@
         <v>74</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="K5" s="1" t="b">
         <v>1</v>
@@ -1179,16 +1227,16 @@
         <v>60</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="42.75" x14ac:dyDescent="0.2">
@@ -1217,7 +1265,7 @@
         <v>75</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="K6" s="1" t="b">
         <v>1</v>
@@ -1259,16 +1307,16 @@
         <v>61</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="57" x14ac:dyDescent="0.2">
@@ -1297,7 +1345,7 @@
         <v>76</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="K7" s="1" t="b">
         <v>1</v>
@@ -1339,16 +1387,16 @@
         <v>60</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="57" x14ac:dyDescent="0.2">
@@ -1377,7 +1425,7 @@
         <v>77</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="K8" s="1" t="b">
         <v>1</v>
@@ -1419,16 +1467,16 @@
         <v>93</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="71.25" x14ac:dyDescent="0.2">
@@ -1457,7 +1505,7 @@
         <v>78</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="K9" s="1" t="b">
         <v>1</v>
@@ -1499,16 +1547,16 @@
         <v>60</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="71.25" x14ac:dyDescent="0.2">
@@ -1537,7 +1585,7 @@
         <v>79</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="K10" s="1" t="b">
         <v>1</v>
@@ -1579,21 +1627,21 @@
         <v>93</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>71</v>
+        <v>133</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="B11" s="2">
         <v>4007</v>
@@ -1617,7 +1665,7 @@
         <v>80</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="K11" s="1" t="b">
         <v>1</v>
@@ -1659,16 +1707,16 @@
         <v>93</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:28" ht="57" x14ac:dyDescent="0.2">
@@ -1697,7 +1745,7 @@
         <v>81</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="K12" s="1" t="b">
         <v>1</v>
@@ -1739,16 +1787,16 @@
         <v>61</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
